--- a/保费金额列举.xlsx
+++ b/保费金额列举.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Benjamin N\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Document\Universe\Build\Tools\moto_ocr\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2798CF9A-9FD4-46AA-8B84-1E7807B27CC0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28935C3F-E3B5-48FA-BB4F-ADE009EC3122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22276" windowHeight="13276" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6" uniqueCount="6">
   <si>
     <t>总金额</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -43,19 +43,11 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>256+tax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>356+tax</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>3*(12-dd+1)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>36(0)</t>
+    <t>456+tax</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -381,13 +373,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D8"/>
-  <sheetFormatPr defaultRowHeight="13.9" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:D7"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="4" max="4" width="12.59765625" customWidth="1"/>
+    <col min="4" max="4" width="12.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -401,7 +393,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A2">
         <v>356</v>
       </c>
@@ -415,88 +407,74 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A3">
-        <v>256</v>
+        <v>456</v>
       </c>
       <c r="B3">
         <v>156</v>
       </c>
       <c r="C3">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D3">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A4">
-        <v>204</v>
+        <v>304</v>
       </c>
       <c r="B4">
         <v>104</v>
       </c>
       <c r="C4">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="D4">
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A5">
-        <v>304</v>
+        <v>404</v>
       </c>
       <c r="B5">
         <v>104</v>
       </c>
       <c r="C5">
-        <v>200</v>
+        <v>300</v>
       </c>
       <c r="D5">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A6">
-        <v>392</v>
+        <v>492</v>
       </c>
       <c r="B6">
         <v>156</v>
       </c>
       <c r="C6">
-        <v>200</v>
-      </c>
-      <c r="D6" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.4">
+        <v>300</v>
+      </c>
+      <c r="D6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B7">
         <v>156</v>
       </c>
       <c r="C7">
-        <v>100</v>
+        <v>300</v>
       </c>
       <c r="D7" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.4">
-      <c r="A8" t="s">
-        <v>5</v>
-      </c>
-      <c r="B8">
-        <v>156</v>
-      </c>
-      <c r="C8">
-        <v>200</v>
-      </c>
-      <c r="D8" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
     </row>
   </sheetData>
